--- a/hardware/bom/bom_completo.xlsx
+++ b/hardware/bom/bom_completo.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\56973\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\56973\Desktop\TEI-201-Secci-n-4-Grupo-9\hardware\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5162035E-1286-494D-92AC-6266D5C1F6A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F724DD2F-E7E7-49DD-88E7-97934E747A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="15192" windowHeight="10836" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -222,15 +222,9 @@
     <t>Genérico</t>
   </si>
   <si>
-    <t>https://cdn.sparkfun.com/datasheets/Sensors/ForceFlex/hx711_english.pdf</t>
-  </si>
-  <si>
     <t>Kuongshun</t>
   </si>
   <si>
-    <t>https://cdn.sparkfun.com/assets/1/9/7/7/b/loadsensor.pdf</t>
-  </si>
-  <si>
     <t>Solo materiales usados hasta ahora. Se agregarán filas a medida que avance el proyecto.</t>
   </si>
   <si>
@@ -238,6 +232,12 @@
   </si>
   <si>
     <t>Código</t>
+  </si>
+  <si>
+    <t>celda_carga_datasheet.pdf</t>
+  </si>
+  <si>
+    <t>HX711_datasheet.pdf</t>
   </si>
 </sst>
 </file>
@@ -246,7 +246,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -501,7 +501,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -796,7 +796,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -819,7 +819,7 @@
         <v>6</v>
       </c>
       <c r="G6" s="21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>7</v>
@@ -867,7 +867,7 @@
         <v>9600</v>
       </c>
       <c r="K7" s="26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
@@ -887,7 +887,7 @@
         <v>16</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G8" s="30">
         <v>1314</v>
@@ -903,7 +903,7 @@
         <v>2300</v>
       </c>
       <c r="K8" s="26" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
@@ -923,7 +923,7 @@
         <v>19</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G9" s="31">
         <v>1345</v>
@@ -993,7 +993,7 @@
         <v>25</v>
       </c>
       <c r="F11" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11" s="30">
         <v>1513</v>
@@ -1133,7 +1133,7 @@
         <v>34</v>
       </c>
       <c r="F15" s="29" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G15" s="31">
         <v>2933</v>
@@ -1358,10 +1358,10 @@
     <hyperlink ref="H18" r:id="rId11" xr:uid="{71CAD6FB-7BE9-4311-A0E8-DBF4232109F4}"/>
     <hyperlink ref="H17" r:id="rId12" xr:uid="{53B076C8-A86C-4DD1-BB52-DBC9FF15F812}"/>
     <hyperlink ref="H8" r:id="rId13" xr:uid="{8D1F30B4-5155-412F-B4C7-25A1440B90A5}"/>
-    <hyperlink ref="K8" r:id="rId14" xr:uid="{A4F2014C-9C68-4624-8E6F-D14908F084B8}"/>
+    <hyperlink ref="K8" r:id="rId14" display="https://cdn.sparkfun.com/datasheets/Sensors/ForceFlex/hx711_english.pdf" xr:uid="{A4F2014C-9C68-4624-8E6F-D14908F084B8}"/>
     <hyperlink ref="K9" r:id="rId15" xr:uid="{4BC9AD55-2951-4380-9221-75788F7AB2C6}"/>
     <hyperlink ref="K14" r:id="rId16" xr:uid="{2B9A1162-199D-44D6-AFDD-5A58F5B54D69}"/>
-    <hyperlink ref="K7" r:id="rId17" xr:uid="{572B5A09-6DFC-4A5D-8B9C-ACF981F0B084}"/>
+    <hyperlink ref="K7" r:id="rId17" display="https://cdn.sparkfun.com/assets/1/9/7/7/b/loadsensor.pdf" xr:uid="{572B5A09-6DFC-4A5D-8B9C-ACF981F0B084}"/>
     <hyperlink ref="K11" r:id="rId18" xr:uid="{BCD4E10B-FE06-459C-8D59-5A504AA3B0AC}"/>
     <hyperlink ref="K15" r:id="rId19" xr:uid="{95A0A40A-0951-4CF5-BB85-25D1AAE37D48}"/>
   </hyperlinks>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B7" s="8">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Mat",BOM!$B$7:$B$22,$A7)</f>

--- a/hardware/bom/bom_completo.xlsx
+++ b/hardware/bom/bom_completo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\56973\Desktop\TEI-201-Secci-n-4-Grupo-9\hardware\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F724DD2F-E7E7-49DD-88E7-97934E747A52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712A93D2-862D-446E-AEF2-06F74AEEBDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="15192" windowHeight="10836" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1116" yWindow="1116" windowWidth="10524" windowHeight="10836" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="74">
   <si>
     <t>SafeRest - Bill of Materials (BOM)</t>
   </si>
@@ -238,6 +238,30 @@
   </si>
   <si>
     <t>HX711_datasheet.pdf</t>
+  </si>
+  <si>
+    <t>Transistor 2N2222</t>
+  </si>
+  <si>
+    <t>Resistencia 1 kΩ</t>
+  </si>
+  <si>
+    <t>https://hubot.cl/producto/transistor-2n2222-to-92-sku-668h3/</t>
+  </si>
+  <si>
+    <t>https://www.onsemi.com/pdf/datasheet/p2n2222a-d.pdf</t>
+  </si>
+  <si>
+    <t>NPN TO-92, activa el buzzer desde D5</t>
+  </si>
+  <si>
+    <t>1 kΩ, entre D5 y la base del transistor</t>
+  </si>
+  <si>
+    <t>406-1</t>
+  </si>
+  <si>
+    <t>https://hubot.cl/producto/20-resistencias-14w-1-distintos-valores/</t>
   </si>
 </sst>
 </file>
@@ -419,15 +443,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -441,15 +459,6 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -508,6 +517,15 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -795,535 +813,573 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="30" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="21" t="s">
+      <c r="I6" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J6" s="21" t="s">
+      <c r="J6" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="21" t="s">
+      <c r="K6" s="16" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="23">
+      <c r="C7" s="18">
         <v>4</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="F7" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="20">
         <v>599</v>
       </c>
-      <c r="H7" s="26" t="s">
+      <c r="H7" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="22">
         <v>2400</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="23">
         <f t="shared" ref="J7:J22" si="0">IF(I7="",0,C7*I7)</f>
         <v>9600</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="21" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="18">
         <v>1</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="29" t="s">
+      <c r="F8" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="25">
         <v>1314</v>
       </c>
-      <c r="H8" s="26" t="s">
+      <c r="H8" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="22">
         <v>2300</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="23">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="K8" s="26" t="s">
+      <c r="K8" s="21" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="23">
+      <c r="C9" s="18">
         <v>1</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="29" t="s">
+      <c r="F9" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="26">
         <v>1345</v>
       </c>
-      <c r="H9" s="26" t="s">
+      <c r="H9" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="22">
         <v>8490</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="23">
         <f t="shared" si="0"/>
         <v>8490</v>
       </c>
-      <c r="K9" s="26" t="s">
+      <c r="K9" s="21" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="23">
+      <c r="C10" s="18">
         <v>1</v>
       </c>
-      <c r="D10" s="32" t="s">
+      <c r="D10" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="30">
+      <c r="G10" s="25">
         <v>1412</v>
       </c>
-      <c r="H10" s="26" t="s">
+      <c r="H10" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="22">
         <v>3000</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="23">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="K10" s="30"/>
+      <c r="K10" s="25"/>
     </row>
     <row r="11" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="18">
         <v>1</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="29" t="s">
+      <c r="F11" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="25">
         <v>1513</v>
       </c>
-      <c r="H11" s="26" t="s">
+      <c r="H11" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="22">
         <v>4990</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="23">
         <f t="shared" si="0"/>
         <v>4990</v>
       </c>
-      <c r="K11" s="26" t="s">
+      <c r="K11" s="21" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="18">
         <v>1</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="F12" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="30">
+      <c r="G12" s="25">
         <v>1451</v>
       </c>
-      <c r="H12" s="26" t="s">
+      <c r="H12" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="22">
         <v>300</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="23">
         <f>IF(I12="",0,C12*I12)</f>
         <v>300</v>
       </c>
-      <c r="K12" s="30"/>
+      <c r="K12" s="25"/>
     </row>
     <row r="13" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="18">
         <v>1</v>
       </c>
-      <c r="D13" s="32" t="s">
+      <c r="D13" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="24" t="s">
+      <c r="F13" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="25">
         <v>1027</v>
       </c>
-      <c r="H13" s="26" t="s">
+      <c r="H13" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="22">
         <v>100</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="23">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K13" s="30"/>
+      <c r="K13" s="25"/>
     </row>
     <row r="14" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="23">
+      <c r="C14" s="18">
         <v>1</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F14" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="25">
         <v>672</v>
       </c>
-      <c r="H14" s="26" t="s">
+      <c r="H14" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="22">
         <v>4290</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="23">
         <f t="shared" si="0"/>
         <v>4290</v>
       </c>
-      <c r="K14" s="26" t="s">
+      <c r="K14" s="21" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="23">
+      <c r="C15" s="18">
         <v>1</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="29" t="s">
+      <c r="F15" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="26">
         <v>2933</v>
       </c>
-      <c r="H15" s="26" t="s">
+      <c r="H15" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="33">
+      <c r="I15" s="28">
         <v>2000</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="23">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="K15" s="26" t="s">
+      <c r="K15" s="21" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="23">
+      <c r="C16" s="18">
         <v>1</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F16" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="26">
         <v>1226</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H16" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="22">
         <v>1500</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="23">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="K16" s="30"/>
+      <c r="K16" s="25"/>
     </row>
     <row r="17" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="23">
+      <c r="C17" s="18">
         <v>1</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="24" t="s">
+      <c r="F17" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="25">
         <v>453</v>
       </c>
-      <c r="H17" s="26" t="s">
+      <c r="H17" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="22">
         <v>5600</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="23">
         <f t="shared" si="0"/>
         <v>5600</v>
       </c>
-      <c r="K17" s="30"/>
+      <c r="K17" s="25"/>
     </row>
     <row r="18" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="18">
         <v>1</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="22"/>
-      <c r="F18" s="24" t="s">
+      <c r="E18" s="17"/>
+      <c r="F18" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="34" t="s">
+      <c r="G18" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="26" t="s">
+      <c r="H18" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="27">
+      <c r="I18" s="22">
         <v>1690</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="23">
         <f t="shared" si="0"/>
         <v>1690</v>
       </c>
-      <c r="K18" s="30"/>
+      <c r="K18" s="25"/>
     </row>
     <row r="19" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="18">
         <v>1</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="24" t="s">
+      <c r="F19" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="31">
+      <c r="G19" s="26">
         <v>1135</v>
       </c>
-      <c r="H19" s="26" t="s">
+      <c r="H19" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="27">
+      <c r="I19" s="22">
         <v>2500</v>
       </c>
-      <c r="J19" s="28">
+      <c r="J19" s="23">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="K19" s="30"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="20">
+      <c r="K19" s="25"/>
+    </row>
+    <row r="20" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="18">
+        <v>1</v>
+      </c>
+      <c r="D20" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="25">
+        <v>668</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="22">
+        <v>160</v>
+      </c>
+      <c r="J20" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="18"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="15">
+        <v>160</v>
+      </c>
+      <c r="K20" s="21" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="18">
+        <v>1</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F21" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="I21" s="22">
+        <v>600</v>
+      </c>
+      <c r="J21" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K21" s="13"/>
+        <v>600</v>
+      </c>
+      <c r="K21" s="25"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
       <c r="F22" s="13"/>
       <c r="G22" s="13"/>
       <c r="H22" s="13"/>
@@ -1335,12 +1391,12 @@
       <c r="K22" s="13"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="J23" s="5">
+      <c r="J23" s="3">
         <f>SUM(J7:J22)</f>
-        <v>46360</v>
+        <v>47120</v>
       </c>
     </row>
   </sheetData>
@@ -1364,9 +1420,12 @@
     <hyperlink ref="K7" r:id="rId17" display="https://cdn.sparkfun.com/assets/1/9/7/7/b/loadsensor.pdf" xr:uid="{572B5A09-6DFC-4A5D-8B9C-ACF981F0B084}"/>
     <hyperlink ref="K11" r:id="rId18" xr:uid="{BCD4E10B-FE06-459C-8D59-5A504AA3B0AC}"/>
     <hyperlink ref="K15" r:id="rId19" xr:uid="{95A0A40A-0951-4CF5-BB85-25D1AAE37D48}"/>
+    <hyperlink ref="H20" r:id="rId20" xr:uid="{5B5673BD-E618-47DD-A5D2-662C2BDDA43C}"/>
+    <hyperlink ref="K20" r:id="rId21" xr:uid="{83D76DB4-DB31-4B4A-A5B8-194700E1D3E4}"/>
+    <hyperlink ref="H21" r:id="rId22" xr:uid="{BD3401A2-019C-47D3-B331-1716ABCF8479}"/>
   </hyperlinks>
   <pageMargins left="0.19685039370078741" right="0" top="0.35433070866141736" bottom="0.19685039370078741" header="0" footer="0"/>
-  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId20"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId23"/>
 </worksheet>
 </file>
 
@@ -1385,126 +1444,126 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Mat",BOM!$B$7:$B$22,$A4)</f>
         <v>8490</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Control",BOM!$B$7:$B$22,$A4)</f>
         <v>4990</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="6">
         <f>B4+C4</f>
         <v>13480</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Mat",BOM!$B$7:$B$22,$A5)</f>
         <v>11900</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Control",BOM!$B$7:$B$22,$A5)</f>
         <v>0</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D5" s="6">
         <f>B5+C5</f>
         <v>11900</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B6" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Mat",BOM!$B$7:$B$22,$A6)</f>
         <v>0</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Control",BOM!$B$7:$B$22,$A6)</f>
         <v>300</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="6">
         <f>B6+C6</f>
         <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B7" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Mat",BOM!$B$7:$B$22,$A7)</f>
         <v>0</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Control",BOM!$B$7:$B$22,$A7)</f>
         <v>0</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="6">
         <f>B7+C7</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Mat",BOM!$B$7:$B$22,$A8)</f>
         <v>3000</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="6">
         <f>SUMIFS(BOM!$J$7:$J$22,BOM!$A$7:$A$22,"Control",BOM!$B$7:$B$22,$A8)</f>
-        <v>17680</v>
-      </c>
-      <c r="D8" s="8">
+        <v>18440</v>
+      </c>
+      <c r="D8" s="6">
         <f>B8+C8</f>
-        <v>20680</v>
+        <v>21440</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="9" t="s">
+      <c r="A9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="8">
         <f>SUM(B4:B8)</f>
         <v>23390</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="8">
         <f>SUM(C4:C8)</f>
-        <v>22970</v>
-      </c>
-      <c r="D9" s="10">
+        <v>23730</v>
+      </c>
+      <c r="D9" s="8">
         <f>SUM(D4:D8)</f>
-        <v>46360</v>
+        <v>47120</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="10">
         <f>D9-BOM!J23</f>
         <v>0</v>
       </c>

--- a/hardware/bom/bom_completo.xlsx
+++ b/hardware/bom/bom_completo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\56973\Desktop\TEI-201-Secci-n-4-Grupo-9\hardware\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{712A93D2-862D-446E-AEF2-06F74AEEBDDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8FACF6-B981-4FBB-BE40-72D3899B093F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1116" yWindow="1116" windowWidth="10524" windowHeight="10836" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -252,9 +252,6 @@
     <t>https://www.onsemi.com/pdf/datasheet/p2n2222a-d.pdf</t>
   </si>
   <si>
-    <t>NPN TO-92, activa el buzzer desde D5</t>
-  </si>
-  <si>
     <t>1 kΩ, entre D5 y la base del transistor</t>
   </si>
   <si>
@@ -262,6 +259,9 @@
   </si>
   <si>
     <t>https://hubot.cl/producto/20-resistencias-14w-1-distintos-valores/</t>
+  </si>
+  <si>
+    <t>NPN TO-92, activa el buzzer desde D5 (datasheet de la variante P2N2222A)</t>
   </si>
 </sst>
 </file>
@@ -272,7 +272,7 @@
     <numFmt numFmtId="164" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -317,12 +317,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Segoe UI"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color rgb="FF050505"/>
       <name val="Arial"/>
@@ -351,6 +345,19 @@
       <i/>
       <sz val="10"/>
       <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -441,9 +448,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -477,54 +484,39 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -813,7 +805,7 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="22" t="s">
         <v>61</v>
       </c>
     </row>
@@ -852,527 +844,527 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="17" t="s">
+    <row r="7" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="26">
         <v>4</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="17">
         <v>599</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="25" t="s">
         <v>44</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="27">
         <v>2400</v>
       </c>
-      <c r="J7" s="23">
+      <c r="J7" s="28">
         <f t="shared" ref="J7:J22" si="0">IF(I7="",0,C7*I7)</f>
         <v>9600</v>
       </c>
-      <c r="K7" s="21" t="s">
+      <c r="K7" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+    <row r="8" spans="1:11" ht="84" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="26">
         <v>1</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="21">
         <v>1314</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="27">
         <v>2300</v>
       </c>
-      <c r="J8" s="23">
+      <c r="J8" s="28">
         <f t="shared" si="0"/>
         <v>2300</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
+    <row r="9" spans="1:11" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="26">
         <v>1</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="F9" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="18">
         <v>1345</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="27">
         <v>8490</v>
       </c>
-      <c r="J9" s="23">
+      <c r="J9" s="28">
         <f t="shared" si="0"/>
         <v>8490</v>
       </c>
-      <c r="K9" s="21" t="s">
+      <c r="K9" s="25" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+    <row r="10" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="26">
         <v>1</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="21">
         <v>1412</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="27">
         <v>3000</v>
       </c>
-      <c r="J10" s="23">
+      <c r="J10" s="28">
         <f t="shared" si="0"/>
         <v>3000</v>
       </c>
-      <c r="K10" s="25"/>
-    </row>
-    <row r="11" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
+      <c r="K10" s="21"/>
+    </row>
+    <row r="11" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A11" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="18">
+      <c r="C11" s="26">
         <v>1</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="21">
         <v>1513</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="27">
         <v>4990</v>
       </c>
-      <c r="J11" s="23">
+      <c r="J11" s="28">
         <f t="shared" si="0"/>
         <v>4990</v>
       </c>
-      <c r="K11" s="21" t="s">
+      <c r="K11" s="25" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="26">
         <v>1</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="21">
         <v>1451</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="27">
         <v>300</v>
       </c>
-      <c r="J12" s="23">
+      <c r="J12" s="28">
         <f>IF(I12="",0,C12*I12)</f>
         <v>300</v>
       </c>
-      <c r="K12" s="25"/>
-    </row>
-    <row r="13" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A13" s="17" t="s">
+      <c r="K12" s="21"/>
+    </row>
+    <row r="13" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A13" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="26">
         <v>1</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="21">
         <v>1027</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="25" t="s">
         <v>51</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="27">
         <v>100</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="28">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="K13" s="25"/>
-    </row>
-    <row r="14" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="K13" s="21"/>
+    </row>
+    <row r="14" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="26">
         <v>1</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="21">
         <v>672</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="H14" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="27">
         <v>4290</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="28">
         <f t="shared" si="0"/>
         <v>4290</v>
       </c>
-      <c r="K14" s="21" t="s">
+      <c r="K14" s="25" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="17" t="s">
+    <row r="15" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A15" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="18">
+      <c r="C15" s="26">
         <v>1</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="E15" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F15" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="18">
         <v>2933</v>
       </c>
-      <c r="H15" s="21" t="s">
+      <c r="H15" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="20">
         <v>2000</v>
       </c>
-      <c r="J15" s="23">
+      <c r="J15" s="28">
         <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="K15" s="21" t="s">
+      <c r="K15" s="25" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+    <row r="16" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A16" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="26">
         <v>1</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="17" t="s">
+      <c r="E16" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="18">
         <v>1226</v>
       </c>
-      <c r="H16" s="21" t="s">
+      <c r="H16" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="27">
         <v>1500</v>
       </c>
-      <c r="J16" s="23">
+      <c r="J16" s="28">
         <f t="shared" si="0"/>
         <v>1500</v>
       </c>
-      <c r="K16" s="25"/>
-    </row>
-    <row r="17" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="17" t="s">
+      <c r="K16" s="21"/>
+    </row>
+    <row r="17" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="17" t="s">
+      <c r="B17" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="26">
         <v>1</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="17" t="s">
+      <c r="E17" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="21">
         <v>453</v>
       </c>
-      <c r="H17" s="21" t="s">
+      <c r="H17" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="27">
         <v>5600</v>
       </c>
-      <c r="J17" s="23">
+      <c r="J17" s="28">
         <f t="shared" si="0"/>
         <v>5600</v>
       </c>
-      <c r="K17" s="25"/>
-    </row>
-    <row r="18" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="K17" s="21"/>
+    </row>
+    <row r="18" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="B18" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="26">
         <v>1</v>
       </c>
-      <c r="D18" s="17" t="s">
+      <c r="D18" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="17"/>
-      <c r="F18" s="19" t="s">
+      <c r="E18" s="19"/>
+      <c r="F18" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G18" s="29" t="s">
+      <c r="G18" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="21" t="s">
+      <c r="H18" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="27">
         <v>1690</v>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="28">
         <f t="shared" si="0"/>
         <v>1690</v>
       </c>
-      <c r="K18" s="25"/>
-    </row>
-    <row r="19" spans="1:11" ht="72" x14ac:dyDescent="0.3">
-      <c r="A19" s="17" t="s">
+      <c r="K18" s="21"/>
+    </row>
+    <row r="19" spans="1:11" ht="66" x14ac:dyDescent="0.3">
+      <c r="A19" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="26">
         <v>1</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="E19" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="18">
         <v>1135</v>
       </c>
-      <c r="H19" s="21" t="s">
+      <c r="H19" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="27">
         <v>2500</v>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="28">
         <f t="shared" si="0"/>
         <v>2500</v>
       </c>
-      <c r="K19" s="25"/>
-    </row>
-    <row r="20" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+      <c r="K19" s="21"/>
+    </row>
+    <row r="20" spans="1:11" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="26">
         <v>1</v>
       </c>
-      <c r="D20" s="31" t="s">
+      <c r="D20" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="19" t="s">
+      <c r="E20" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="21">
         <v>668</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="27">
         <v>160</v>
       </c>
-      <c r="J20" s="23">
+      <c r="J20" s="28">
         <f t="shared" si="0"/>
         <v>160</v>
       </c>
-      <c r="K20" s="21" t="s">
+      <c r="K20" s="25" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="17" t="s">
+    <row r="21" spans="1:11" ht="52.8" x14ac:dyDescent="0.3">
+      <c r="A21" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="26">
         <v>1</v>
       </c>
-      <c r="D21" s="31" t="s">
+      <c r="D21" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="E21" s="33" t="s">
+      <c r="E21" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="F21" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="29" t="s">
+      <c r="H21" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="H21" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="I21" s="22">
+      <c r="I21" s="27">
         <v>600</v>
       </c>
-      <c r="J21" s="23">
+      <c r="J21" s="28">
         <f t="shared" si="0"/>
         <v>600</v>
       </c>
-      <c r="K21" s="25"/>
+      <c r="K21" s="21"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
